--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00759B-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00759B-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9093ED9-BA76-481C-AC8D-108D36592B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{37CBD019-B428-41DA-ADA5-65C37AFAF5BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{F4120077-0618-4645-A915-32A331598028}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{AD3C53DD-1CAF-45EA-B40C-922599A1EA2F}"/>
   </bookViews>
   <sheets>
     <sheet name="00759B-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1627,25 +1627,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C09C0804-6878-4771-8555-8448C99F2EE6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03622DFD-4BD5-42F5-8613-BD6BFB0B60AF}">
   <dimension ref="A1:R43"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1673,7 +1673,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1703,7 +1703,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1749,7 +1749,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1799,7 +1799,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1853,7 +1853,7 @@
         <v>4.49</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1879,7 +1879,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1935,7 +1935,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1989,7 +1989,7 @@
         <v>4.59</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -2045,7 +2045,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
@@ -2213,7 +2213,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="51">
         <v>2024</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>4.2699999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>27</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>27</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>27</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>27</v>
       </c>
@@ -2491,7 +2491,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="49">
         <v>2023</v>
       </c>
@@ -2545,7 +2545,7 @@
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>27</v>
       </c>
@@ -2601,7 +2601,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>27</v>
       </c>
@@ -2657,7 +2657,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>27</v>
       </c>
@@ -2713,7 +2713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>27</v>
       </c>
@@ -2769,7 +2769,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="51">
         <v>2022</v>
       </c>
@@ -2823,7 +2823,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>27</v>
       </c>
@@ -2879,7 +2879,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>27</v>
       </c>
@@ -2935,7 +2935,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>27</v>
       </c>
@@ -2991,7 +2991,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>27</v>
       </c>
@@ -3047,7 +3047,7 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="49">
         <v>2021</v>
       </c>
@@ -3101,7 +3101,7 @@
         <v>3.09</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>27</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>27</v>
       </c>
@@ -3213,7 +3213,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>27</v>
       </c>
@@ -3269,7 +3269,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>27</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="51">
         <v>2020</v>
       </c>
@@ -3379,7 +3379,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>27</v>
       </c>
@@ -3435,7 +3435,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>27</v>
       </c>
@@ -3491,7 +3491,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>27</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>27</v>
       </c>
@@ -3603,7 +3603,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="49">
         <v>2019</v>
       </c>
@@ -3657,7 +3657,7 @@
         <v>4.3600000000000003</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
         <v>27</v>
       </c>
@@ -3713,7 +3713,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
         <v>27</v>
       </c>
@@ -3769,7 +3769,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
         <v>27</v>
       </c>
@@ -3825,7 +3825,7 @@
         <v>2.81</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
         <v>27</v>
       </c>
@@ -3881,7 +3881,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="51" t="s">
         <v>80</v>
       </c>
